--- a/data/staffInfo.xlsx
+++ b/data/staffInfo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>userName</t>
   </si>
@@ -31,18 +31,6 @@
     <t>Age</t>
   </si>
   <si>
-    <t>sreng_senghuy</t>
-  </si>
-  <si>
-    <t>senghuy123</t>
-  </si>
-  <si>
-    <t>sreng senghuy</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
     <t>mengly</t>
   </si>
   <si>
@@ -50,6 +38,12 @@
   </si>
   <si>
     <t>male</t>
+  </si>
+  <si>
+    <t>bunsak</t>
+  </si>
+  <si>
+    <t>kong bunsak</t>
   </si>
 </sst>
 </file>
@@ -384,13 +378,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
       </c>
       <c r="E2">
         <v>19</v>
@@ -398,19 +392,19 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
